--- a/multi/det_gemini_domain.xlsx
+++ b/multi/det_gemini_domain.xlsx
@@ -407,10 +407,10 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -446,10 +446,10 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
